--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92567839291</v>
+        <v>46157.93097260539</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93097260539</v>
+        <v>46157.93172231196</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93172231196</v>
+        <v>46157.9339961072</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9339961072</v>
+        <v>46157.93717532306</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93717532306</v>
+        <v>46158.2821596266</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2821596266</v>
+        <v>46158.29680658677</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29680658677</v>
+        <v>46158.29814257396</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29814257396</v>
+        <v>46158.33386976832</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33386976832</v>
+        <v>46158.36856694127</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/31. Энерго-газ-Ноябрьск (тепловая энергия)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36856694127</v>
+        <v>46158.37287473863</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
